--- a/excel/pacifico-ayacucho_ruta_proxima_semana.xlsx
+++ b/excel/pacifico-ayacucho_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,19 +428,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,8 +495,7496 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C004247257</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10423495079</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HUARCAYA RIVEROS RAQUELINA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>JR MARTE N° 198</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C004034163</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>28315692</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>INFANZON HUAMAN MARLENY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BARRIO ANDAMARCA MZ K LT 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C001418061</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80031570</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VALENCIA CHAUCA ELSA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PROLONGACION ALAMEDA MZ A LT NRO. 35 URB. FRENTE GRIFO CHIPANA Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C001516464</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10283139099</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COELLO ARANGO KARINA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>JR. ESPANA NRO. 147 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C001470203</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28313423</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FERNANDEZ MAURICIO MERCEDES</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>JR. LOS AMANTES NRO. 385 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C001750362</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28276995</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERNA LOPEZ HILDA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>JR. PROGRESO MZ E LT NRO. 7 INT. A Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C001710289</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28809377</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>QUISPE POMA YANINA YANET</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>JR. PROGRESO NRO. 10 Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C000922539</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10283133031</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIAZ HUAMAN KETY</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>JR. LOS AMANTES NRO. 192 URB. SAN JUAN BAUTISTA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C001179420</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28287018</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MOISES ARANGO ZENOBIA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>JR. MARIANO BELLIDO NRO. 195 URB. SAN JUAN BAUTISTA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C000920929</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7925601</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QUISPE YANCE GUILLERMA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>JR. MADRID NRO. 107-A Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C004212319</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43969662</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ ARANGO YOVANA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>JR MURIVE 115</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C004061319</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28295343</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ONCEBAY TIPE NANCY BETTY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>JR 28 DE JULIO Nº 413</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C001381787</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28289814</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>QUISPE HUAMAN HERMENEGILDA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MCDO. CENTRAL PTO H NRO. 36 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C001522174</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20602667571</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FASTER D´SAR E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>JR. MANCO CAPAC NRO. 753 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C001570612</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44750769</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SILVA ROMANI FRIDS STIVEN</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>JR. HUANCASOLAR NRO. 140 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C004036080</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42273878</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LLAMOCCA HUAMAN SOFIA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>JR UNSCH Nº 423</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C000921532</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>28286546</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>QUISPE YUPANQUI ANGELICA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>JR. CESAR VALLEJO NRO. 490 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C001761074</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>76375108</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CUBA RODRIGUEZ LUANA MAYHOMI</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>JR. CESAR VALLEJO NRO. 419 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C004040102</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>41699913</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ROJAS GUILLEN EDY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>JR JOSE MARIA ARGUEDAS Nº 405</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C004036090</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>70397133</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AGUIRRE ORE KELLY ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AV QUINUAPATA Nº 527</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C001616485</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>42640154</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PARIONA VENTURA NORMA CLAUDIA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NERY GARCIA MZO LT NRO. 7 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C001676779</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>40650475</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TRELLES CURI CARMEN ROXANA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>JR. CAHUIDE NRO. 306 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C000921638</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28249573</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MOROTE BEDRIÑANA CARMEN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>JR. GRAU N650 NRO. 650 MZA. MAZAA049 URB. JR GRAU Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C001761087</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>28239783</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ROCA DE QUISPE TERESA AURELIA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AV. 13 DE ABRIL Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C001755234</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>20611020181</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RYZOM E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AV. 24 DE JUNIO NRO. 323 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C001510419</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>41976213</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SUICA FLORES REINALDA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>JR. WARI NRO. 118 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C001745134</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>28215123</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MARTINEZ DE PARIONA VICTORIA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>JR. LA MAR NRO. 320 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C000921771</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>28226300</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALVARO HUYHUA ELSA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>AV. AVE 24 DE JUNIO NRO. 301 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C001672276</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>71287874</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>GALINDO MICUILLA MARIBEL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AV. AV MELENDEZ MZ C NRO. 8 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C001004515</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10417282497</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SALVATIERRA GARAMENDI NELIDA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>JR. MADRID NRO. 191 URB. CERCADO Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C004037163</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>28248646</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CORDERO LUYA MARIA ISABEL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PASJ ROMERO Nº 118</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C001642394</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>28313709</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CRUZ TINEO CELIA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>JR. MICAELA BASTIDAS NRO. 250 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C001752238</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>48424583</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ZURITA ESPINOZA NOEMI YOVANNA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AV. AMANCAES NRO. 130 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C001737067</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>28306538</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>GUTIERREZ YUCRA ANTONIA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AV. AV AMANCAES NRO. 213 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C001761011</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>28272842</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MUCHA VALDIVIA FORTUNATA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AV. EJERCITO NRO. 189 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C000920785</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10101822783</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>GAMONAL CANGANA VIDAL DAVID</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AV. EJERCITO NRO. 221 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C001453581</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>28228169</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ ZAGA VILMA ERNISTINA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>AV. AMANCAES NRO. 375 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C001742948</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>70213842</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CONDE GARCIA EDY KARINA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>AV. JOSE CARLOS MARIATEGUI Nº NRO. 102 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C001704147</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>70049641</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MENDOZA GODOY NIELS ERICKSON</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AV. RAMON CASTILLA NRO. 885 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C001761019</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>28233290</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PEREZ ARONE DONATILDA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>AV. LOS INCAS NRO. 362 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C001440914</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>42838332</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LUJAN PAUCCA DORIS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>MERCADO LAS AMERICAS PUESTO N NRO. 605 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C000920972</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>10282239308</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PISCO DE RAMIREZ LEONOR</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>AV. AVE SAN FRANCISCO MYI L3 MZA. MAZAA490 LOTE. 3 URB. LOS OLIVOS Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C001736856</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>28225442</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MENDOZA VILLAR ROBERTA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>JR. CONSTITUCION S/N Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C004034155</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>28211616</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>MARTINEZ VIVANCO ROSA SONIA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>LOS ANDES MZ F LT 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C001746142</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>28313677</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ARANGO PRADO ERLINDA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AV. KUIS CARRANZA N° NRO. 231 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C004048651</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>28267445</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AYALA MENDOZA HUGO GODOFREDO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AV LOS INKAS Nº 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C001401796</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>28245238</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CORAS DE OCHOA FRANCISCA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>JR. MIRAFLORES NRO. 155 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C001761088</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>70406169</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>VILCA AGUIRRE JUAN MARCOS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AV. 13 DE ABRIL Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C004245993</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>45240259</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>LLAMOCCA GODOY MARLENY</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PJE. LOS ANDES S/N</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C001526289</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>40580149</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>TORRES QUICHCA ERLINDA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>JR. LOS ANGELES NRO. 132 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C000920460</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>28309719</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MENDOZA VALLEJO MAXIMINA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AV. ANDES NRO. 324 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C001412904</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>28274855</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MORALES OCHOA DOLORES SERAFINA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>JR. MORRO DE ARICA MZ Q LT NRO. 3 MZA. Q LOTE. 3 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C004189002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>42670023</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MUÑOZ GUTIERREZ FRINE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>MORO DE ARICA N° 103</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C004051478</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>73749686</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>TORRE NAJARRO PAULA YOSELIN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AV LIBERTADORES MZ S LT 04</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C004239754</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10468041567</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DIAZ LOZANO MAIKOL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>BARRIO LA LIBERTAD MANZ J LOTE 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C001633485</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>42332861</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>FLORES PIRCA OLGA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AAHH ALTO PERU MZA. X LOTE. 1 URB. PUEBLO LIBRE Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C004213977</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>46569747</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SULCA YAURI ERIKA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ASOCIACION PISCOTAMBO MZQ1LT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C001660020</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>46618041</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CUBA PARIONA BEATRIZ VEDALINA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PISCO TAMBO MZA. LL LOTE. 02 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C001622301</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>74219502</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>RUA ESCRIBA ROCIO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ASOC BASILIO AUQUI MZH LT NRO. 09 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C001674581</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>40495238</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CORONADO YUPANQUI YANETT MAGALI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>AV. ASOC BASILIO AUQUI NRO. 280 MZA. H LOTE. 16 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C001746522</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>28220211</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>LANDEO ROJAS LEONOR</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>BASILIO AUQUI S/N Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C004247260</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>71242202</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>YUPANQUI VALERIANO DIANA ISABEL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>MERCADO NERY PSTO 105</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C001374040</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>28243075</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>LEANDRO GOMEZ ANGEL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ASOC MECANICOS MZ LL LT NRO. 4 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C001564790</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>80503574</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CALDERON YUCRA MECHE DOTI</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>JR. TOMAS UBILLUS NRO. 377 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C001623695</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>10429854160</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ESPINO GUTIERREZ MARISOL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>MZA. L LOTE. 02 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C001712450</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>41050565</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SABOYA SANCHEZ MARNITH</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AV. EMADI NRO. 7 MZA. O Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C001636710</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>10444068065</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SAUÑE GAMBOA KARINA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>JR. MARAVILLAS NRO. 248 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C001216512</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>42557585</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERNA VILCHEZ FRANK</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>JR. JR 22 DE JUNIO NRO. 353 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C001744281</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>45050502</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CCOLLANA VERGARA CRISTINA MAGALY</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>JR. LIBERTAD NRO. 656 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C004042247</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>28310999</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HUACCE ROBLES NANCY</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>JR SOL Nº 203</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C004065151</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>9193489</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CHAVEZ QUINTANILLA DE PAREDES PELAGIA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>JR UNTIVEROS N° 194</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C001454299</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>28288782</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GOMEZ VILCATOMA MARLENI</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>JR. LOS ANDES NRO. 160 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C001761085</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>71988046</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>GARCIA CUADROS EDISON</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>AV. LIBERTADORES MZA. M LOTE. 12 Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C001766330</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>76366763</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SOLIER LOPEZ ELVIS DIEGO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>JR. LOS OLIVOS MZA. O LOTE. 10 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C001413545</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>45650781</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>QUISPE IGNACION MARY LUZ</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>AV. SAN FRANCISCO MZ L2- LT NRO. 04 URB. LOS OLIVOS Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C001676475</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>28603590</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CHAHUA QUISPE MARIA ANTONIA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ASOC LOS OLIVOS MZLL LT NRO. 5 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C001629905</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>42386724</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CACERES CASTILLO JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AV. SAN FRANCISCO MZA. LL2 LOTE. 5 URB. FRENTE A LA CEV PEZ MUDO Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C001373853</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>41644990</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>LLACTAHUAMAN VILLAGARAY LILIANA ISABEL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>JR. ASOC FRANCISCO MELENDEZ NRO. 13 MZA. B URB. PUERTA CE MARIA AUXILIADORA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C001761100</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>28832026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CAMARGO GARIBAY LUCILA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA MZ Y LT NRO. 14 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C001348045</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>28225481</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>BORDA GAMARRA TEODORO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA MZ C1 LT NRO. 11 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>C001718792</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>43535171</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>QUISPE SAYAS YOLANDA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>AV. LAS MALVINAS MZ I LT NRO. 13 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C004038384</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>40821217</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ALANYA CORAS ZORAIDA VICTORIA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>JR LUCIANA MZ M 01 LT 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>C001547166</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>20980895</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>COLLAHUACHO GUTIERREZ JORGE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA S/N Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>C001026130</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>28287708</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ SULCA DIANOT GUADALUPE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA W1 LT1 MZA. 036 URB. LOS OLIVOS Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C004223702</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>46376546</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PACHECO LOPEZ FAVIO DANIEL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA X12 OLIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C001707343</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>40091011</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ROJAS ARAUJO MARCELINO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO LAS AMERICAS PTO N° NRO. 460 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C001006897</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>40934705</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CCORAHUA CARHUAPOMA OLGA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO LAS AMERICAS PTO NRO. 06 PSTO. 06 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C000922323</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>28276976</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>GAVILAN DE CASTILLO TEOFILA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>COOP LIBERTAD DE LAS AMERICAS NRO. 20 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C001730722</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>28223571</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>GUTIERREZ CAMONES VICENTA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>JR. AYACUCHO NRO. 4 MZA. H LOTE. 4 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C001750799</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>71201399</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>BARZOLA AYALA MADELI</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>JR. LOS OLIVOS NRO. 2 INT. A MZA. A1 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C001678316</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>28248575</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CANCHARI DE POMACANCHARI FELICITAS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ASOC LA VICTORIA MZA. H LOTE. 09 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C000921535</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>42522461</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CARHUAPOMA CAYLLAHUA JUDITH YOVANA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>AV. AVE AVLA VICTORIA M-H L-5 MZA. MAZAA150 LOTE. 5 URB. ASOC LA VICTORIA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C001761033</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>45907227</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>MORENO ANCO ANA FELICITAS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>JR. LOS SAUCES MZA. A LOTE. 13 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C001761037</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>70663893</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SOLIER PANIORA LUZ ROSMERY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>AV. FRANCISCO MELENDEZ DE TINAGERA MZA. E LOTE. 02 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C000920889</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>28263051</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>LESCANO CHAVEZ MANUEL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>AV. ABRAHAM BALDELOMAR MZ T LT NRO. 05 URB. VISTA ALEGRE Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C001704319</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>47445140</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ZAPATA ESTRADA MARTIN HUMBERTO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Carmen Alto (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>AV. ABRAHAN VALDELOMAR NRO. 190 Ayacucho-Huamanga-Carmen Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C001463687</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>28200286</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PILLACA LOAYZA INES</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>JR. PROTZEL NRO. 307 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C004186090</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>42432893</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>BORDA PEREZ ESTHER</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>JR MANUEL J POZO N° 231</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C001621604</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>44389419</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>HUAMAN RIVAS ODALIS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>JR. CIRO ALEGRIA NRO. 391 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C001723807</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>48174928</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>VALER ZEA JONATHAN</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>JR. JR CIRO ALEGRIA N° 510 NRO. 510 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C001326505</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>28288795</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>BARBOZA BERNA NANCY</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>JR. SALVADOR CAVERO NRO. 778 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C001744749</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>41406522</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>QUIHUI QUISPE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AV. JR MARIANO MELGAR NRO. 981 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C004203937</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>28276531</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>LOPE CORDOVA DONATILDA FILOMENA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>JR. CIRO ALEGRÍA 1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C001741629</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>74434717</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SULCA FLORES MILUSKA MARISOL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>JR. BARRENECHEA NRO. 568 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C001552897</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>46787305</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ARANGO HINOSTROZA YENNI SUMICO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>JR. F MAÑARICUA NRO. 42 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C001760999</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>40682728</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>FLORES AYALA JEAN PAUL</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>AV. MANUEL ALARCON NRO. 413 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C000922293</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>10282261095</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>GARCIA HUAMAN MARGARITA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>CL. JIR MARIANO MELGAR N1208 NRO. 1208 MZA. MAZAA999 URB. LAS NAZARENAS Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C001637978</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>28287733</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>HUARACA AYLAS HILDA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>JR. JOSE SANTOS CHOCANO NRO. 1291 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C000920240</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>40226853</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>TUCTA MALDONADO ENRIQUETA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>MCDO. MCDO JESUS NAZARENO PTO N NRO. 267 Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C004102336</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>77672724</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>AUCCATOMA TINEO ACBALY DANIELA</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>MERCADO NAZARENAS PUESTO 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C001724263</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>41944549</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ISIDRO BERROCAL NAMBER</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>AV. LOS MUNICIPALES NRO. 13 MZA. G Ayacucho-Huamanga-Jesús Nazareno</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C004093407</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>42322899</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>OLIVARES ROMANI MARILUZ</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Jesús Nazareno (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>ASOC SAN MARTIN DE PORRES MZ K LT 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C001409402</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>28271801</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>YAURI CASTELO BERTHA INES</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>JR. DOMINGO NIETO NRO. 415 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C001748202</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>28274793</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PLANTANOS MENDOZA NORMA ISABEL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>JR. JR MANCO CAPAC NRO. 772 Ayacucho-Huamanga-Ayacucho</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C001546435</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>46011273</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ FLORES YOVANA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>PJE. LOS NOGALES NRO. 130 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C001687540</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>40262505</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PILLACA LOAYZA MARIVEL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>AV. AV EJERCITO NRO. 494 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C001501806</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>45851270</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SANTIAGO BORDA LIDIA DIONISIA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>JR. LOS ROSALES NRO. 293 URB. PARQUE DE LAS BANDERAS Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C001576666</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>73874580</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>OCHOA FLORES PATRICIA JAKELIN</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>AV. AMANCAES NRO. 821 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C004238799</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>28293161</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>MARTINEZ MALLQUI YURIK</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>AV. AMANCAES 928, AYACUCHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C001684337</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>42521546</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>VELARDE PALOMINO TANIA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>AV. RAMON CASTILLA NRO. 932 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C001628299</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>70093026</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>IZQUIERDO ROBLES MILAGROS ISABEL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>AV. ARENALES NRO. 210 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C001682302</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>40603456</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>CALDERON GOMEZ SONIA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ASOC VILLA MILITAR MZA. K LOTE. 01A Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C000920985</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>10282447041</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>VALDEZ DE PILLACA GREGORIA</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>JR. POKRAS NRO. 120 URB. SAN JUAN BAUTISTA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C001748469</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>70173306</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>LEON CHIQUILLAN MIGUIA ROCIO</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>JR. MOCHICA NRO. 106 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C001579492</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>74421207</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CHAVEZ VILLANO YUDIT</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Ayacucho (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>WARI ACCOPAMPA MZ B LT 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C004187981</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>4321251</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>HINOSTROZA GONZALES NESTOR PAULINO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>AV ARENALES N° 397</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C001480509</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>43116379</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>CHAUCA SIMON INELDA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>AV. ARENALES NRO. 432 URB. ARENALES Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C000922489</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>28272964</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>HUAMAN ESCALANTE REINA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>AV. OTR ASOC VIRGEN DEL CARMEN M- MZA. MAZAA003 LOTE. 09 URB. CANAN BAJO Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C001218807</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>41039169</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>HUAMANI QUISPE WILBER</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>LOS JARDINES MZA. B1 LOTE. 10 URB. APROVISA Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C001749402</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>71392849</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>LAHUANA TIPE ALEXIS</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>ASOCAPROVISA MZU LT NRO. 12 INT. A Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C001628135</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>74325607</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>MEDRANO MEDRANO ANABELA JHEIDY</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>AV. 9 DE DICIEMBRE MZA. J LOTE. 01 URB. APROVISA Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C000921258</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>28304601</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ARCCE FLORES SONIA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>AV. 9 DE DICIEMBRE NRO. 139 URB. SAN FRANCISCO Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C001530391</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>43873551</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>CURI VELARDE JOHANNA DAISY</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>AV. NUEVA ESPERANZA NRO. 1000 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C001224875</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>28296761</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>TINEO HINOSTROZA LUCIA</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>AV. 9 DE DICIEMBRE NRO. 479 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C001750103</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>74998369</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>QUISPE MOSCO LUCY</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>JR. ANCAHS NRO. 130 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C004032711</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>42616170</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CHUCHON CARPIO NORMA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>AV 09 DE DICIEMBRE Nº 590</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C001750899</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>31189712</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>MATAMOROS REYNAGA MIRTHA SILVIA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Andrés Avelino Cáceres Dorregaray (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>AV. 09 DE DICIEMBRE NRO. 680 Ayacucho-Huamanga-Andrés Avelino Cáceres Dorregaray</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C004093406</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>10762326995</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>CARDENAS QUISPE GREICY YESENIA</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>AV LAS AMERICAS MZ K LT 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C001638405</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>20607433489</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>MULTIVENTAS VALU E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AV JOSE CARLOS AMREATEGUI N 129</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C001012155</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>41724926</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>POMAHUALLCA ESCUDERO MONICA LORENA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>AV. SAN FRANCISCO NRO. 116 Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C004159620</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>70653760</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>BARZOLA DIPAZ ROXANA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>AV SAN FRANCISCO Nº 116</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C000922564</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>10282710051</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ATACHAO VILCAPOMA MARIA ESTHER</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>LOTE. 03 URB. CIUDAD MAGISTERIAL Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C001749589</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>43056825</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>BELLIDO BEJAR EDIHT</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>AAHHSANTA ROSA MZF LT NRO. 7 INT. B Ayacucho-Huamanga-San Juan Bautista</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PACIFICO AYACUCHO</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C004142705</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>71905320</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>VIVANCO ESCALANTE YASMIN DANAY</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>San Juan Bautista (Huamanga)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>JR LOS CLAVELES N° 122</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>